--- a/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Requirements_Traceability_Matrix.xlsx
+++ b/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Requirements_Traceability_Matrix.xlsx
@@ -480,6 +480,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -649,22 +650,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>API works and is validated but the lecturer page is not built (D-03)</t>
+          <t>API and page work. Slots are published and edited and removed from the page after the D-03 and D-10 fixes</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>TC-03 and TC-18 and TC-19 and TC-20 and TC-25</t>
+          <t>TC-03 and TC-18 and TC-19 and TC-20 and TC-25 and TC-33 and TC-34</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Partially Met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -696,7 +697,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Slots listed correctly but the page does not show the times until D-02 is merged</t>
+          <t>Slots listed correctly and the times show after the D-02 fix</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -706,12 +707,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Partially Met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -790,7 +791,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Cancel works in the page and change works in the API but there is no change button (D-04)</t>
+          <t>Cancel and change both work in the page after the D-04 fix</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -800,12 +801,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Partially Met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -931,7 +932,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Student page works and the lecturer list works in the API but has no page (D-03)</t>
+          <t>Student page and lecturer page both show the bookings after the D-03 fix</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -941,12 +942,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Partially Met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1026,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Slowest page load was 452 ms and slowest API call 19 ms</t>
+          <t>Slowest page load was 389 ms and slowest API call 19 ms</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1072,7 +1073,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>No sideways scrolling on the pages that exist. The lecturer page is not built</t>
+          <t>No sideways scrolling on all five pages at both widths</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1087,7 +1088,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Partially Met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1120,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>All 7 stored passwords are bcrypt hashes. Repeated wrong passwords are not limited (D-06)</t>
+          <t>All 7 stored passwords are bcrypt hashes and repeated wrong passwords are limited after the D-06 fix</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>TC-13</t>
+          <t>TC-13 and TC-30</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1260,7 +1261,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Plain messages and typed text kept. Two small issues logged (D-05 and D-08)</t>
+          <t>Plain messages and typed text kept and a clear message when the session ends after the D-05 and D-08 fixes</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1270,12 +1271,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Partially Met</t>
+          <t>Met</t>
         </is>
       </c>
     </row>

--- a/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Requirements_Traceability_Matrix.xlsx
+++ b/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Requirements_Traceability_Matrix.xlsx
@@ -480,7 +480,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -885,7 +884,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Confirmation and reminder work in preview mode. Real SMTP delivery is still to be tested on the demo laptop</t>
+          <t>Confirmation and reminder work in preview mode and an SMTP test email was received on 23 October. The booking emails are still to be checked on the demo laptop</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Requirements_Traceability_Matrix.xlsx
+++ b/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Requirements_Traceability_Matrix.xlsx
@@ -884,7 +884,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Confirmation and reminder work in preview mode and an SMTP test email was received on 23 October. The booking emails are still to be checked on the demo laptop</t>
+          <t>Confirmation and reminder work in preview mode, an SMTP test email was received on 23 October and the booking emails arrived on the demonstration laptop</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Scripted journey took 1.8 seconds. The timed test with students is planned for Week 5</t>
+          <t>Scripted journey took 1.8 seconds. The bookings were not timed in the user testing on 28 October (4 students and 2 lecturers)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
